--- a/dist/data/events.xlsx
+++ b/dist/data/events.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Codes\Recis React\public\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Codes\r-shs\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A5AAAB2-09C5-4C6B-A836-4682836F6851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C704D912-50B1-4C2E-95F0-B9EEC29308A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="3075" windowWidth="20385" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2460" yWindow="3870" windowWidth="20385" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>name</t>
   </si>
@@ -39,61 +39,34 @@
     <t>link</t>
   </si>
   <si>
-    <t>/Christmas</t>
-  </si>
-  <si>
-    <t>Coming Soon</t>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>Page</t>
+  </si>
+  <si>
+    <t>Gallery</t>
+  </si>
+  <si>
+    <t>/r-shs/Gallery</t>
+  </si>
+  <si>
+    <t>/r-shs/</t>
   </si>
   <si>
     <t>Jingle Joyce</t>
   </si>
   <si>
+    <t>Events</t>
+  </si>
+  <si>
+    <t>/r-shs/Christmas</t>
+  </si>
+  <si>
     <t>Slither Sweetheart</t>
   </si>
   <si>
-    <t>Events</t>
-  </si>
-  <si>
-    <t>MPLS</t>
-  </si>
-  <si>
-    <t>Easter Charity</t>
-  </si>
-  <si>
-    <t>Christmas Charity</t>
-  </si>
-  <si>
-    <t>Ending</t>
-  </si>
-  <si>
-    <t>Done</t>
-  </si>
-  <si>
-    <t>17 Agustus</t>
-  </si>
-  <si>
-    <t>/Valentine</t>
-  </si>
-  <si>
-    <t>/Charity</t>
-  </si>
-  <si>
-    <t>/Mpls</t>
-  </si>
-  <si>
-    <t>/Pensi</t>
-  </si>
-  <si>
-    <t>Home</t>
-  </si>
-  <si>
-    <t>Page</t>
-  </si>
-  <si>
-    <t>//</t>
-  </si>
-  <si>
-    <t>Pensi</t>
+    <t>/r-shs/Valentine</t>
   </si>
 </sst>
 </file>
@@ -135,9 +108,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="28.140625" customWidth="1"/>
@@ -440,111 +412,46 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
         <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/dist/data/events.xlsx
+++ b/dist/data/events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Codes\r-shs\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C704D912-50B1-4C2E-95F0-B9EEC29308A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{827A6B81-E55B-4C0D-B6B5-7B1F8EE026FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2460" yWindow="3870" windowWidth="20385" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/dist/data/events.xlsx
+++ b/dist/data/events.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Codes\r-shs\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{827A6B81-E55B-4C0D-B6B5-7B1F8EE026FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA216346-0BBB-46A6-A3C8-82597BAE36C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2460" yWindow="3870" windowWidth="20385" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9645" yWindow="5670" windowWidth="20385" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>name</t>
   </si>
@@ -67,6 +67,12 @@
   </si>
   <si>
     <t>/r-shs/Valentine</t>
+  </si>
+  <si>
+    <t>Recup</t>
+  </si>
+  <si>
+    <t>/r-shs/Recis-Cup</t>
   </si>
 </sst>
 </file>
@@ -390,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="28.140625" customWidth="1"/>
@@ -454,6 +460,17 @@
         <v>7</v>
       </c>
     </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dist/data/events.xlsx
+++ b/dist/data/events.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Codes\r-shs\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA216346-0BBB-46A6-A3C8-82597BAE36C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27DEB5D6-EE95-4B49-A80C-970ED213EB9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9645" yWindow="5670" windowWidth="20385" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="4515" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>name</t>
   </si>
@@ -54,19 +54,7 @@
     <t>/r-shs/</t>
   </si>
   <si>
-    <t>Jingle Joyce</t>
-  </si>
-  <si>
     <t>Events</t>
-  </si>
-  <si>
-    <t>/r-shs/Christmas</t>
-  </si>
-  <si>
-    <t>Slither Sweetheart</t>
-  </si>
-  <si>
-    <t>/r-shs/Valentine</t>
   </si>
   <si>
     <t>Recup</t>
@@ -396,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="28.140625" customWidth="1"/>
@@ -429,46 +417,24 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
